--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11003"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pc/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40448E9-34E1-9F40-81B1-87CBECBCAEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12465"/>
+    <workbookView xWindow="0" yWindow="1640" windowWidth="28800" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Modèle d'importation" sheetId="1" r:id="rId1"/>
@@ -15,8 +21,8 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modèle d''importation'!$A$1:$J$2</definedName>
     <definedName name="HiddenSheet1">[1]HiddenSheet1!$A$1:$A$661</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modèle d''importation'!$A$1:$J$2</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -67,7 +73,7 @@
         <sz val="18"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="SimSun"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>⚠</t>
     </r>
@@ -77,7 +83,7 @@
         <sz val="18"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Veuillez lire ce guide pour remplir votre commande avec succès</t>
     </r>
@@ -87,7 +93,7 @@
         <sz val="18"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -97,7 +103,7 @@
         <sz val="18"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="SimSun"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>⚠</t>
     </r>
@@ -107,7 +113,7 @@
         <sz val="18"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t>️</t>
     </r>
@@ -119,7 +125,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Le tableau est divisé en deux parties principales：</t>
     </r>
@@ -129,7 +135,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -140,7 +146,7 @@
         <sz val="14"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">Informations client + </t>
     </r>
@@ -150,7 +156,7 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Détails de la commande</t>
     </r>
@@ -162,7 +168,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Waybill:</t>
     </r>
@@ -171,7 +177,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>facultatif; Numéro de lettre de transport logistique, par segment de numéro non attribué par faster, s'il vous plaît contacter le vendeur si nécessaire.</t>
     </r>
@@ -189,7 +195,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Nom</t>
     </r>
@@ -199,7 +205,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -209,7 +215,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Nom complet du destinataire</t>
     </r>
@@ -230,7 +236,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>obligatoire</t>
     </r>
@@ -242,7 +248,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">S.O.
 </t>
@@ -252,7 +258,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Votre numéro de commande, les doublons ne sont pas autorisés.</t>
     </r>
@@ -267,7 +273,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Téléphone</t>
     </r>
@@ -277,7 +283,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -287,7 +293,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Numéro de téléphone du destinataire, longueur du numéro : 10 chiffres</t>
     </r>
@@ -299,7 +305,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Nom de la marchandise
 </t>
@@ -309,7 +315,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Nom ou description de l'article</t>
     </r>
@@ -321,7 +327,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">Zone
 </t>
@@ -331,7 +337,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Veuillez sélectionner le district dans la liste des zones disponibles. Si vous avez des difficultés à choisir le district, vous pouvez le saisir manuellement. Cependant, veuillez noter qu'en cas d'erreur de saisie, il sera nécessaire de le corriger lors de l'importation pour que le téléchargement de la commande soit réussi.</t>
     </r>
@@ -343,7 +349,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Montant total</t>
     </r>
@@ -353,7 +359,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -363,7 +369,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Si ce n'est pas un paiement à la livraison ou pas de COD ，le montant peut être saisi à 0</t>
     </r>
@@ -378,7 +384,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">Autoriser l'ouverture du colis ou non </t>
     </r>
@@ -388,7 +394,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -398,7 +404,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">Si vous n'autorisez pas le client à ouvrir le colis, laissez vide ou sélectionnez 'Non'. </t>
     </r>
@@ -410,7 +416,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Adresse complète</t>
     </r>
@@ -420,7 +426,7 @@
         <sz val="13"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -430,7 +436,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>adresse complète du destinataire</t>
     </r>
@@ -5254,26 +5260,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="44">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5287,48 +5287,48 @@
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="SimSun"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -5342,34 +5342,34 @@
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FF808080"/>
       <name val="宋体"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0563C1"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -5393,153 +5393,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5547,36 +5411,36 @@
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5609,210 +5473,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.5"/>
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -5929,342 +5607,55 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="34" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="34" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6279,70 +5670,79 @@
     <xf numFmtId="0" fontId="18" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="Normal 2" xfId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="43" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="44" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="45" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="46" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="47" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="48" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="49" builtinId="52"/>
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="法文"/>
@@ -6622,75 +6022,366 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5583333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.4416666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="31.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.8916666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.225" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.225" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.1083333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5583333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="28" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="54" spans="1:10">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30" t="s">
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+    </row>
+    <row r="2" spans="1:10" ht="45">
+      <c r="A2" s="23"/>
+      <c r="B2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="13" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6698,140 +6389,148 @@
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576">
-      <formula1>Région!$A$2:$A$1521</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I3:I130">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="I3:I130" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>Région!$A$2:$A$1521</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40.1333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18.025" customWidth="1"/>
-    <col min="3" max="3" width="3.65833333333333" customWidth="1"/>
-    <col min="4" max="4" width="51.4916666666667" customWidth="1"/>
-    <col min="5" max="5" width="22.0916666666667" customWidth="1"/>
+    <col min="1" max="1" width="40.1640625" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" customWidth="1"/>
+    <col min="4" max="4" width="51.5" customWidth="1"/>
+    <col min="5" max="5" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" spans="1:5">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" ht="24">
+      <c r="A1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="2" ht="53" customHeight="1" spans="1:5">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+    </row>
+    <row r="2" spans="1:5" ht="53" customHeight="1">
+      <c r="A2" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" ht="53" customHeight="1" spans="1:5">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+    </row>
+    <row r="3" spans="1:5" ht="53" customHeight="1">
+      <c r="A3" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="15"/>
-    </row>
-    <row r="5" ht="47.25" spans="1:5">
-      <c r="A5" s="16" t="s">
+      <c r="E4" s="34"/>
+    </row>
+    <row r="5" spans="1:5" ht="52">
+      <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="19" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="60" spans="1:5">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:5" ht="68">
+      <c r="A6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19" t="s">
+      <c r="C6" s="7"/>
+      <c r="D6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="180" spans="1:5">
-      <c r="A7" s="22" t="s">
+    <row r="7" spans="1:5" ht="221">
+      <c r="A7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="22" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" ht="45.75" spans="1:5">
-      <c r="A8" s="23" t="s">
+    <row r="8" spans="1:5" ht="50">
+      <c r="A8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="22" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="31.5" spans="1:5">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:5" ht="34">
+      <c r="A9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="22" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -6844,24 +6543,23 @@
     <mergeCell ref="D4:E4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A8" location="区域!A1" display="here."/>
+    <hyperlink ref="A8" location="区域!A1" display="here." xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B2200"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.5583333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:2">
+    <row r="1" spans="1:2" ht="30">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -19029,49 +18727,49 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="1522" spans="2:2">
+    <row r="1522" spans="1:2">
       <c r="B1522" s="3"/>
     </row>
-    <row r="1523" spans="2:2">
+    <row r="1523" spans="1:2">
       <c r="B1523" s="3"/>
     </row>
-    <row r="1524" spans="2:2">
+    <row r="1524" spans="1:2">
       <c r="B1524" s="3"/>
     </row>
-    <row r="1525" spans="2:2">
+    <row r="1525" spans="1:2">
       <c r="B1525" s="3"/>
     </row>
-    <row r="1526" spans="2:2">
+    <row r="1526" spans="1:2">
       <c r="B1526" s="3"/>
     </row>
-    <row r="1527" spans="2:2">
+    <row r="1527" spans="1:2">
       <c r="B1527" s="3"/>
     </row>
-    <row r="1528" spans="2:2">
+    <row r="1528" spans="1:2">
       <c r="B1528" s="3"/>
     </row>
-    <row r="1529" spans="2:2">
+    <row r="1529" spans="1:2">
       <c r="B1529" s="3"/>
     </row>
-    <row r="1530" spans="2:2">
+    <row r="1530" spans="1:2">
       <c r="B1530" s="3"/>
     </row>
-    <row r="1531" spans="2:2">
+    <row r="1531" spans="1:2">
       <c r="B1531" s="3"/>
     </row>
-    <row r="1532" spans="2:2">
+    <row r="1532" spans="1:2">
       <c r="B1532" s="3"/>
     </row>
-    <row r="1533" spans="2:2">
+    <row r="1533" spans="1:2">
       <c r="B1533" s="3"/>
     </row>
-    <row r="1534" spans="2:2">
+    <row r="1534" spans="1:2">
       <c r="B1534" s="3"/>
     </row>
-    <row r="1535" spans="2:2">
+    <row r="1535" spans="1:2">
       <c r="B1535" s="3"/>
     </row>
-    <row r="1536" spans="2:2">
+    <row r="1536" spans="1:2">
       <c r="B1536" s="3"/>
     </row>
     <row r="1537" spans="2:2">
@@ -21068,6 +20766,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>